--- a/Production/waken.xlsx
+++ b/Production/waken.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_07_18" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_08_12" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="456">
   <si>
     <t>Designator</t>
   </si>
@@ -919,7 +919,7 @@
     <t>24.638mm</t>
   </si>
   <si>
-    <t>SW1</t>
+    <t>RST</t>
   </si>
   <si>
     <t>KMR223GLFG</t>
@@ -949,7 +949,7 @@
     <t>https://item.szlcsc.com/datasheet/KMR223GLFG/222108.html</t>
   </si>
   <si>
-    <t>SW2</t>
+    <t>BOOT</t>
   </si>
   <si>
     <t>28.575mm</t>
@@ -973,13 +973,13 @@
     <t>KEY-SMD_K2-1845SA-D4SW-04</t>
   </si>
   <si>
-    <t>37.084mm</t>
+    <t>37.465mm</t>
   </si>
   <si>
     <t>28.067mm</t>
   </si>
   <si>
-    <t>35.807mm</t>
+    <t>36.188mm</t>
   </si>
   <si>
     <t>25.437mm</t>
@@ -997,15 +997,9 @@
     <t>SW4</t>
   </si>
   <si>
-    <t>37.465mm</t>
-  </si>
-  <si>
     <t>5.969mm</t>
   </si>
   <si>
-    <t>36.188mm</t>
-  </si>
-  <si>
     <t>3.339mm</t>
   </si>
   <si>
@@ -1270,7 +1264,7 @@
     <t>SMD,D=2mm</t>
   </si>
   <si>
-    <t>GND</t>
+    <t>U10</t>
   </si>
   <si>
     <t>17.018mm</t>
@@ -1364,6 +1358,27 @@
   </si>
   <si>
     <t>21.229mm</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>24.511mm</t>
+  </si>
+  <si>
+    <t>5.461mm</t>
+  </si>
+  <si>
+    <t>24.269mm</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>26.162mm</t>
+  </si>
+  <si>
+    <t>25.92mm</t>
   </si>
 </sst>
 </file>
@@ -1740,7 +1755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S63"/>
+  <dimension ref="A1:S65"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="19" width="20" customWidth="1"/>
@@ -4471,22 +4486,22 @@
         <v>319</v>
       </c>
       <c r="D47" t="s">
+        <v>320</v>
+      </c>
+      <c r="E47" t="s">
         <v>328</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
+        <v>320</v>
+      </c>
+      <c r="G47" t="s">
+        <v>328</v>
+      </c>
+      <c r="H47" t="s">
+        <v>322</v>
+      </c>
+      <c r="I47" t="s">
         <v>329</v>
-      </c>
-      <c r="F47" t="s">
-        <v>328</v>
-      </c>
-      <c r="G47" t="s">
-        <v>329</v>
-      </c>
-      <c r="H47" t="s">
-        <v>330</v>
-      </c>
-      <c r="I47" t="s">
-        <v>331</v>
       </c>
       <c r="J47">
         <v>4</v>
@@ -4521,31 +4536,31 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>330</v>
+      </c>
+      <c r="B48" t="s">
+        <v>331</v>
+      </c>
+      <c r="C48" t="s">
         <v>332</v>
       </c>
-      <c r="B48" t="s">
+      <c r="D48" t="s">
         <v>333</v>
       </c>
-      <c r="C48" t="s">
+      <c r="E48" t="s">
         <v>334</v>
       </c>
-      <c r="D48" t="s">
+      <c r="F48" t="s">
+        <v>333</v>
+      </c>
+      <c r="G48" t="s">
+        <v>334</v>
+      </c>
+      <c r="H48" t="s">
         <v>335</v>
       </c>
-      <c r="E48" t="s">
+      <c r="I48" t="s">
         <v>336</v>
-      </c>
-      <c r="F48" t="s">
-        <v>335</v>
-      </c>
-      <c r="G48" t="s">
-        <v>336</v>
-      </c>
-      <c r="H48" t="s">
-        <v>337</v>
-      </c>
-      <c r="I48" t="s">
-        <v>338</v>
       </c>
       <c r="J48">
         <v>25</v>
@@ -4560,51 +4575,51 @@
         <v>26</v>
       </c>
       <c r="N48" t="s">
+        <v>337</v>
+      </c>
+      <c r="O48" t="s">
+        <v>27</v>
+      </c>
+      <c r="P48" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q48" t="s">
         <v>339</v>
       </c>
-      <c r="O48" t="s">
-        <v>27</v>
-      </c>
-      <c r="P48" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>341</v>
-      </c>
       <c r="R48" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="S48" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>340</v>
+      </c>
+      <c r="B49" t="s">
+        <v>341</v>
+      </c>
+      <c r="C49" t="s">
         <v>342</v>
       </c>
-      <c r="B49" t="s">
+      <c r="D49" t="s">
         <v>343</v>
       </c>
-      <c r="C49" t="s">
+      <c r="E49" t="s">
         <v>344</v>
       </c>
-      <c r="D49" t="s">
+      <c r="F49" t="s">
+        <v>343</v>
+      </c>
+      <c r="G49" t="s">
+        <v>344</v>
+      </c>
+      <c r="H49" t="s">
         <v>345</v>
       </c>
-      <c r="E49" t="s">
+      <c r="I49" t="s">
         <v>346</v>
-      </c>
-      <c r="F49" t="s">
-        <v>345</v>
-      </c>
-      <c r="G49" t="s">
-        <v>346</v>
-      </c>
-      <c r="H49" t="s">
-        <v>347</v>
-      </c>
-      <c r="I49" t="s">
-        <v>348</v>
       </c>
       <c r="J49">
         <v>49</v>
@@ -4619,51 +4634,51 @@
         <v>26</v>
       </c>
       <c r="N49" t="s">
+        <v>347</v>
+      </c>
+      <c r="O49" t="s">
+        <v>27</v>
+      </c>
+      <c r="P49" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q49" t="s">
         <v>349</v>
       </c>
-      <c r="O49" t="s">
-        <v>27</v>
-      </c>
-      <c r="P49" t="s">
+      <c r="R49" t="s">
         <v>350</v>
       </c>
-      <c r="Q49" t="s">
-        <v>351</v>
-      </c>
-      <c r="R49" t="s">
-        <v>352</v>
-      </c>
       <c r="S49" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>351</v>
+      </c>
+      <c r="B50" t="s">
+        <v>352</v>
+      </c>
+      <c r="C50" t="s">
         <v>353</v>
       </c>
-      <c r="B50" t="s">
+      <c r="D50" t="s">
         <v>354</v>
       </c>
-      <c r="C50" t="s">
+      <c r="E50" t="s">
         <v>355</v>
       </c>
-      <c r="D50" t="s">
+      <c r="F50" t="s">
+        <v>354</v>
+      </c>
+      <c r="G50" t="s">
+        <v>355</v>
+      </c>
+      <c r="H50" t="s">
         <v>356</v>
       </c>
-      <c r="E50" t="s">
+      <c r="I50" t="s">
         <v>357</v>
-      </c>
-      <c r="F50" t="s">
-        <v>356</v>
-      </c>
-      <c r="G50" t="s">
-        <v>357</v>
-      </c>
-      <c r="H50" t="s">
-        <v>358</v>
-      </c>
-      <c r="I50" t="s">
-        <v>359</v>
       </c>
       <c r="J50">
         <v>9</v>
@@ -4678,51 +4693,51 @@
         <v>26</v>
       </c>
       <c r="N50" t="s">
+        <v>358</v>
+      </c>
+      <c r="O50" t="s">
+        <v>27</v>
+      </c>
+      <c r="P50" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q50" t="s">
         <v>360</v>
       </c>
-      <c r="O50" t="s">
-        <v>27</v>
-      </c>
-      <c r="P50" t="s">
-        <v>361</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>362</v>
-      </c>
       <c r="R50" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="S50" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>361</v>
+      </c>
+      <c r="B51" t="s">
+        <v>362</v>
+      </c>
+      <c r="C51" t="s">
         <v>363</v>
       </c>
-      <c r="B51" t="s">
+      <c r="D51" t="s">
         <v>364</v>
       </c>
-      <c r="C51" t="s">
+      <c r="E51" t="s">
         <v>365</v>
       </c>
-      <c r="D51" t="s">
+      <c r="F51" t="s">
+        <v>364</v>
+      </c>
+      <c r="G51" t="s">
+        <v>365</v>
+      </c>
+      <c r="H51" t="s">
         <v>366</v>
       </c>
-      <c r="E51" t="s">
+      <c r="I51" t="s">
         <v>367</v>
-      </c>
-      <c r="F51" t="s">
-        <v>366</v>
-      </c>
-      <c r="G51" t="s">
-        <v>367</v>
-      </c>
-      <c r="H51" t="s">
-        <v>368</v>
-      </c>
-      <c r="I51" t="s">
-        <v>369</v>
       </c>
       <c r="J51">
         <v>8</v>
@@ -4737,51 +4752,51 @@
         <v>26</v>
       </c>
       <c r="N51" t="s">
+        <v>368</v>
+      </c>
+      <c r="O51" t="s">
+        <v>27</v>
+      </c>
+      <c r="P51" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q51" t="s">
         <v>370</v>
       </c>
-      <c r="O51" t="s">
-        <v>27</v>
-      </c>
-      <c r="P51" t="s">
-        <v>371</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>372</v>
-      </c>
       <c r="R51" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="S51" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>371</v>
+      </c>
+      <c r="B52" t="s">
+        <v>372</v>
+      </c>
+      <c r="C52" t="s">
         <v>373</v>
       </c>
-      <c r="B52" t="s">
+      <c r="D52" t="s">
         <v>374</v>
       </c>
-      <c r="C52" t="s">
+      <c r="E52" t="s">
         <v>375</v>
       </c>
-      <c r="D52" t="s">
+      <c r="F52" t="s">
+        <v>374</v>
+      </c>
+      <c r="G52" t="s">
+        <v>375</v>
+      </c>
+      <c r="H52" t="s">
         <v>376</v>
       </c>
-      <c r="E52" t="s">
+      <c r="I52" t="s">
         <v>377</v>
-      </c>
-      <c r="F52" t="s">
-        <v>376</v>
-      </c>
-      <c r="G52" t="s">
-        <v>377</v>
-      </c>
-      <c r="H52" t="s">
-        <v>378</v>
-      </c>
-      <c r="I52" t="s">
-        <v>379</v>
       </c>
       <c r="J52">
         <v>8</v>
@@ -4796,51 +4811,51 @@
         <v>26</v>
       </c>
       <c r="N52" t="s">
+        <v>378</v>
+      </c>
+      <c r="O52" t="s">
+        <v>27</v>
+      </c>
+      <c r="P52" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q52" t="s">
         <v>380</v>
       </c>
-      <c r="O52" t="s">
-        <v>27</v>
-      </c>
-      <c r="P52" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>382</v>
-      </c>
       <c r="R52" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="S52" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>381</v>
+      </c>
+      <c r="B53" t="s">
+        <v>382</v>
+      </c>
+      <c r="C53" t="s">
         <v>383</v>
       </c>
-      <c r="B53" t="s">
+      <c r="D53" t="s">
         <v>384</v>
       </c>
-      <c r="C53" t="s">
+      <c r="E53" t="s">
         <v>385</v>
       </c>
-      <c r="D53" t="s">
+      <c r="F53" t="s">
+        <v>384</v>
+      </c>
+      <c r="G53" t="s">
+        <v>385</v>
+      </c>
+      <c r="H53" t="s">
         <v>386</v>
       </c>
-      <c r="E53" t="s">
+      <c r="I53" t="s">
         <v>387</v>
-      </c>
-      <c r="F53" t="s">
-        <v>386</v>
-      </c>
-      <c r="G53" t="s">
-        <v>387</v>
-      </c>
-      <c r="H53" t="s">
-        <v>388</v>
-      </c>
-      <c r="I53" t="s">
-        <v>389</v>
       </c>
       <c r="J53">
         <v>14</v>
@@ -4855,51 +4870,51 @@
         <v>26</v>
       </c>
       <c r="N53" t="s">
+        <v>388</v>
+      </c>
+      <c r="O53" t="s">
+        <v>27</v>
+      </c>
+      <c r="P53" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q53" t="s">
         <v>390</v>
       </c>
-      <c r="O53" t="s">
-        <v>27</v>
-      </c>
-      <c r="P53" t="s">
-        <v>391</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>392</v>
-      </c>
       <c r="R53" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="S53" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>391</v>
+      </c>
+      <c r="B54" t="s">
+        <v>392</v>
+      </c>
+      <c r="C54" t="s">
         <v>393</v>
       </c>
-      <c r="B54" t="s">
+      <c r="D54" t="s">
         <v>394</v>
       </c>
-      <c r="C54" t="s">
+      <c r="E54" t="s">
         <v>395</v>
       </c>
-      <c r="D54" t="s">
+      <c r="F54" t="s">
+        <v>394</v>
+      </c>
+      <c r="G54" t="s">
+        <v>395</v>
+      </c>
+      <c r="H54" t="s">
         <v>396</v>
       </c>
-      <c r="E54" t="s">
+      <c r="I54" t="s">
         <v>397</v>
-      </c>
-      <c r="F54" t="s">
-        <v>396</v>
-      </c>
-      <c r="G54" t="s">
-        <v>397</v>
-      </c>
-      <c r="H54" t="s">
-        <v>398</v>
-      </c>
-      <c r="I54" t="s">
-        <v>399</v>
       </c>
       <c r="J54">
         <v>5</v>
@@ -4914,51 +4929,51 @@
         <v>26</v>
       </c>
       <c r="N54" t="s">
+        <v>398</v>
+      </c>
+      <c r="O54" t="s">
+        <v>27</v>
+      </c>
+      <c r="P54" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q54" t="s">
         <v>400</v>
       </c>
-      <c r="O54" t="s">
-        <v>27</v>
-      </c>
-      <c r="P54" t="s">
-        <v>401</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>402</v>
-      </c>
       <c r="R54" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="S54" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>401</v>
+      </c>
+      <c r="B55" t="s">
+        <v>402</v>
+      </c>
+      <c r="C55" t="s">
         <v>403</v>
       </c>
-      <c r="B55" t="s">
+      <c r="D55" t="s">
         <v>404</v>
-      </c>
-      <c r="C55" t="s">
-        <v>405</v>
-      </c>
-      <c r="D55" t="s">
-        <v>406</v>
       </c>
       <c r="E55" t="s">
         <v>190</v>
       </c>
       <c r="F55" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="G55" t="s">
         <v>190</v>
       </c>
       <c r="H55" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="I55" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="J55">
         <v>10</v>
@@ -4973,51 +4988,51 @@
         <v>26</v>
       </c>
       <c r="N55" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="O55" t="s">
         <v>27</v>
       </c>
       <c r="P55" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q55" t="s">
         <v>12</v>
       </c>
       <c r="R55" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="S55" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>409</v>
+      </c>
+      <c r="B56" t="s">
+        <v>410</v>
+      </c>
+      <c r="C56" t="s">
         <v>411</v>
       </c>
-      <c r="B56" t="s">
+      <c r="D56" t="s">
         <v>412</v>
       </c>
-      <c r="C56" t="s">
+      <c r="E56" t="s">
         <v>413</v>
       </c>
-      <c r="D56" t="s">
-        <v>414</v>
-      </c>
-      <c r="E56" t="s">
-        <v>415</v>
-      </c>
       <c r="F56" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G56" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H56" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I56" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -5032,51 +5047,51 @@
         <v>26</v>
       </c>
       <c r="N56" t="s">
+        <v>414</v>
+      </c>
+      <c r="O56" t="s">
+        <v>27</v>
+      </c>
+      <c r="P56" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q56" t="s">
         <v>416</v>
       </c>
-      <c r="O56" t="s">
-        <v>27</v>
-      </c>
-      <c r="P56" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>418</v>
-      </c>
       <c r="R56" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="S56" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B57" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C57" t="s">
+        <v>411</v>
+      </c>
+      <c r="D57" t="s">
+        <v>418</v>
+      </c>
+      <c r="E57" t="s">
         <v>413</v>
       </c>
-      <c r="D57" t="s">
-        <v>420</v>
-      </c>
-      <c r="E57" t="s">
-        <v>415</v>
-      </c>
       <c r="F57" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G57" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H57" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I57" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -5091,51 +5106,51 @@
         <v>26</v>
       </c>
       <c r="N57" t="s">
+        <v>414</v>
+      </c>
+      <c r="O57" t="s">
+        <v>27</v>
+      </c>
+      <c r="P57" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q57" t="s">
         <v>416</v>
       </c>
-      <c r="O57" t="s">
-        <v>27</v>
-      </c>
-      <c r="P57" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>418</v>
-      </c>
       <c r="R57" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="S57" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>419</v>
+      </c>
+      <c r="B58" t="s">
+        <v>410</v>
+      </c>
+      <c r="C58" t="s">
+        <v>411</v>
+      </c>
+      <c r="D58" t="s">
+        <v>420</v>
+      </c>
+      <c r="E58" t="s">
         <v>421</v>
       </c>
-      <c r="B58" t="s">
-        <v>412</v>
-      </c>
-      <c r="C58" t="s">
-        <v>413</v>
-      </c>
-      <c r="D58" t="s">
-        <v>422</v>
-      </c>
-      <c r="E58" t="s">
-        <v>423</v>
-      </c>
       <c r="F58" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G58" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H58" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I58" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -5150,51 +5165,51 @@
         <v>26</v>
       </c>
       <c r="N58" t="s">
+        <v>414</v>
+      </c>
+      <c r="O58" t="s">
+        <v>27</v>
+      </c>
+      <c r="P58" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q58" t="s">
         <v>416</v>
       </c>
-      <c r="O58" t="s">
-        <v>27</v>
-      </c>
-      <c r="P58" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>418</v>
-      </c>
       <c r="R58" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="S58" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B59" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C59" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D59" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E59" t="s">
+        <v>421</v>
+      </c>
+      <c r="F59" t="s">
         <v>423</v>
       </c>
-      <c r="F59" t="s">
-        <v>425</v>
-      </c>
       <c r="G59" t="s">
+        <v>421</v>
+      </c>
+      <c r="H59" t="s">
         <v>423</v>
       </c>
-      <c r="H59" t="s">
-        <v>425</v>
-      </c>
       <c r="I59" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -5209,51 +5224,51 @@
         <v>26</v>
       </c>
       <c r="N59" t="s">
+        <v>414</v>
+      </c>
+      <c r="O59" t="s">
+        <v>27</v>
+      </c>
+      <c r="P59" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q59" t="s">
         <v>416</v>
       </c>
-      <c r="O59" t="s">
-        <v>27</v>
-      </c>
-      <c r="P59" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>418</v>
-      </c>
       <c r="R59" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="S59" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>424</v>
+      </c>
+      <c r="B60" t="s">
+        <v>425</v>
+      </c>
+      <c r="C60" t="s">
         <v>426</v>
       </c>
-      <c r="B60" t="s">
+      <c r="D60" t="s">
         <v>427</v>
       </c>
-      <c r="C60" t="s">
+      <c r="E60" t="s">
         <v>428</v>
       </c>
-      <c r="D60" t="s">
+      <c r="F60" t="s">
+        <v>427</v>
+      </c>
+      <c r="G60" t="s">
+        <v>428</v>
+      </c>
+      <c r="H60" t="s">
         <v>429</v>
       </c>
-      <c r="E60" t="s">
+      <c r="I60" t="s">
         <v>430</v>
-      </c>
-      <c r="F60" t="s">
-        <v>429</v>
-      </c>
-      <c r="G60" t="s">
-        <v>430</v>
-      </c>
-      <c r="H60" t="s">
-        <v>431</v>
-      </c>
-      <c r="I60" t="s">
-        <v>432</v>
       </c>
       <c r="J60">
         <v>20</v>
@@ -5268,51 +5283,51 @@
         <v>193</v>
       </c>
       <c r="N60" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="O60" t="s">
         <v>27</v>
       </c>
       <c r="P60" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q60" t="s">
         <v>12</v>
       </c>
       <c r="R60" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="S60" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>433</v>
+      </c>
+      <c r="B61" t="s">
+        <v>434</v>
+      </c>
+      <c r="C61" t="s">
         <v>435</v>
       </c>
-      <c r="B61" t="s">
+      <c r="D61" t="s">
         <v>436</v>
       </c>
-      <c r="C61" t="s">
+      <c r="E61" t="s">
         <v>437</v>
       </c>
-      <c r="D61" t="s">
+      <c r="F61" t="s">
+        <v>436</v>
+      </c>
+      <c r="G61" t="s">
+        <v>437</v>
+      </c>
+      <c r="H61" t="s">
+        <v>436</v>
+      </c>
+      <c r="I61" t="s">
         <v>438</v>
-      </c>
-      <c r="E61" t="s">
-        <v>439</v>
-      </c>
-      <c r="F61" t="s">
-        <v>438</v>
-      </c>
-      <c r="G61" t="s">
-        <v>439</v>
-      </c>
-      <c r="H61" t="s">
-        <v>438</v>
-      </c>
-      <c r="I61" t="s">
-        <v>440</v>
       </c>
       <c r="J61">
         <v>2</v>
@@ -5327,27 +5342,27 @@
         <v>26</v>
       </c>
       <c r="N61" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="O61" t="s">
         <v>27</v>
       </c>
       <c r="P61" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="Q61" t="s">
         <v>69</v>
       </c>
       <c r="R61" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="S61" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B62" t="s">
         <v>279</v>
@@ -5356,22 +5371,22 @@
         <v>230</v>
       </c>
       <c r="D62" t="s">
+        <v>443</v>
+      </c>
+      <c r="E62" t="s">
+        <v>444</v>
+      </c>
+      <c r="F62" t="s">
+        <v>443</v>
+      </c>
+      <c r="G62" t="s">
+        <v>444</v>
+      </c>
+      <c r="H62" t="s">
+        <v>443</v>
+      </c>
+      <c r="I62" t="s">
         <v>445</v>
-      </c>
-      <c r="E62" t="s">
-        <v>446</v>
-      </c>
-      <c r="F62" t="s">
-        <v>445</v>
-      </c>
-      <c r="G62" t="s">
-        <v>446</v>
-      </c>
-      <c r="H62" t="s">
-        <v>445</v>
-      </c>
-      <c r="I62" t="s">
-        <v>447</v>
       </c>
       <c r="J62">
         <v>2</v>
@@ -5406,7 +5421,7 @@
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s">
         <v>82</v>
@@ -5415,22 +5430,22 @@
         <v>32</v>
       </c>
       <c r="D63" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E63" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F63" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G63" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H63" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="I63" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J63">
         <v>2</v>
@@ -5461,6 +5476,124 @@
       </c>
       <c r="S63" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>449</v>
+      </c>
+      <c r="B64" t="s">
+        <v>237</v>
+      </c>
+      <c r="C64" t="s">
+        <v>230</v>
+      </c>
+      <c r="D64" t="s">
+        <v>450</v>
+      </c>
+      <c r="E64" t="s">
+        <v>451</v>
+      </c>
+      <c r="F64" t="s">
+        <v>450</v>
+      </c>
+      <c r="G64" t="s">
+        <v>451</v>
+      </c>
+      <c r="H64" t="s">
+        <v>452</v>
+      </c>
+      <c r="I64" t="s">
+        <v>451</v>
+      </c>
+      <c r="J64">
+        <v>2</v>
+      </c>
+      <c r="K64" t="s">
+        <v>192</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64" t="s">
+        <v>26</v>
+      </c>
+      <c r="N64" t="s">
+        <v>241</v>
+      </c>
+      <c r="O64" t="s">
+        <v>27</v>
+      </c>
+      <c r="P64" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>38</v>
+      </c>
+      <c r="R64" t="s">
+        <v>243</v>
+      </c>
+      <c r="S64" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>453</v>
+      </c>
+      <c r="B65" t="s">
+        <v>237</v>
+      </c>
+      <c r="C65" t="s">
+        <v>230</v>
+      </c>
+      <c r="D65" t="s">
+        <v>454</v>
+      </c>
+      <c r="E65" t="s">
+        <v>451</v>
+      </c>
+      <c r="F65" t="s">
+        <v>454</v>
+      </c>
+      <c r="G65" t="s">
+        <v>451</v>
+      </c>
+      <c r="H65" t="s">
+        <v>455</v>
+      </c>
+      <c r="I65" t="s">
+        <v>451</v>
+      </c>
+      <c r="J65">
+        <v>2</v>
+      </c>
+      <c r="K65" t="s">
+        <v>192</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" t="s">
+        <v>241</v>
+      </c>
+      <c r="O65" t="s">
+        <v>27</v>
+      </c>
+      <c r="P65" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>38</v>
+      </c>
+      <c r="R65" t="s">
+        <v>243</v>
+      </c>
+      <c r="S65" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
